--- a/Project_Accounts.xlsx
+++ b/Project_Accounts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Sooqna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Sooqna-2026\Sooqna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF9906C-F0BB-46AE-8EFC-73E4211D4EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FD059B-5B43-4F7D-8502-161D91BEACC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{78B6B321-109A-4F24-AF21-35591DEC6D24}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{78B6B321-109A-4F24-AF21-35591DEC6D24}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Service</t>
   </si>
@@ -46,13 +46,19 @@
   </si>
   <si>
     <t>K+a9@$v*[7;n[B![</t>
+  </si>
+  <si>
+    <t>pgAdmin</t>
+  </si>
+  <si>
+    <t>StrongPass123!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,6 +80,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -118,11 +130,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent6" xfId="1" builtinId="49"/>
@@ -475,9 +488,13 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">

--- a/Project_Accounts.xlsx
+++ b/Project_Accounts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Sooqna-2026\Sooqna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FD059B-5B43-4F7D-8502-161D91BEACC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A7E5A6-EC10-4917-832B-B09D3BC958AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{78B6B321-109A-4F24-AF21-35591DEC6D24}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{78B6B321-109A-4F24-AF21-35591DEC6D24}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Service</t>
   </si>
@@ -52,6 +52,12 @@
   </si>
   <si>
     <t>StrongPass123!</t>
+  </si>
+  <si>
+    <t>port</t>
+  </si>
+  <si>
+    <t>postgresql</t>
   </si>
 </sst>
 </file>
@@ -504,15 +510,23 @@
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2">
+        <v>5433</v>
+      </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -584,6 +598,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{F379C979-1479-4FC0-858D-BD1D0704CE6D}"/>
+    <hyperlink ref="C5" r:id="rId2" display="mailto:K+a9@$v*[7;n[B![" xr:uid="{9BF92C1A-EEB7-41B3-8851-775DDFE3C7DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
